--- a/data/kilometrajes_latest.xlsx
+++ b/data/kilometrajes_latest.xlsx
@@ -455,11 +455,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24173.94</v>
+        <v>25129.32</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-08 14:36:00</t>
+          <t>2026-10-09 14:17:52</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -467,7 +467,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -479,11 +479,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>358288.94</v>
+        <v>358346.78</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-08 14:39:39</t>
+          <t>2026-10-09 14:17:55</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -491,7 +491,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -503,11 +503,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>220496</v>
+        <v>221664.94</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-08 14:41:08</t>
+          <t>2026-10-09 14:17:23</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -515,7 +515,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -527,11 +527,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1707544.62</v>
+        <v>1707903.5</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-08 14:41:59</t>
+          <t>2026-10-09 14:14:13</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -539,7 +539,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -551,11 +551,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>144177.53</v>
+        <v>144275</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-08 14:41:53</t>
+          <t>2026-10-09 14:16:19</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -563,7 +563,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -575,11 +575,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>190461.33</v>
+        <v>190548.59</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-08 14:38:17</t>
+          <t>2026-10-09 14:15:19</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -587,7 +587,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -599,11 +599,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>787496.1899999999</v>
+        <v>788261.6899999999</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-08 14:37:45</t>
+          <t>2026-10-09 14:18:20</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -611,7 +611,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -623,11 +623,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1344277</v>
+        <v>1345253.38</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-08 14:28:37</t>
+          <t>2026-10-09 14:17:51</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -635,7 +635,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -647,11 +647,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>179613.43</v>
+        <v>179669.59</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-08 14:40:49</t>
+          <t>2026-10-09 14:16:35</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -659,7 +659,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -671,11 +671,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1251863.5</v>
+        <v>1253042.12</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-08 14:42:17</t>
+          <t>2026-10-09 14:16:07</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -683,7 +683,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -695,11 +695,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>126829.78</v>
+        <v>126895.13</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-08 14:42:30</t>
+          <t>2026-10-09 14:17:36</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -707,7 +707,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -719,11 +719,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>356865.84</v>
+        <v>357324</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-08 14:42:36</t>
+          <t>2026-10-09 14:18:26</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -743,11 +743,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>198204.67</v>
+        <v>199372.08</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-10-08 14:42:00</t>
+          <t>2026-10-09 14:18:26</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -755,7 +755,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -767,11 +767,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>288460.66</v>
+        <v>288619.91</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-10-08 14:40:43</t>
+          <t>2026-10-09 14:18:20</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -791,11 +791,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>237208.17</v>
+        <v>237661.25</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-08 14:42:33</t>
+          <t>2026-10-09 14:17:24</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -803,7 +803,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -815,11 +815,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>593192.09</v>
+        <v>594369.41</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-10-08 14:42:36</t>
+          <t>2026-10-09 14:17:33</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -827,7 +827,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -839,11 +839,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>301834.81</v>
+        <v>303012.22</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-08 14:42:36</t>
+          <t>2026-10-09 14:17:27</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -851,7 +851,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -863,11 +863,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>19108.55</v>
+        <v>20290.07</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-10-08 14:40:58</t>
+          <t>2026-10-09 14:17:51</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -875,7 +875,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -887,11 +887,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>98322.17</v>
+        <v>98390.82000000001</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-10-08 14:42:51</t>
+          <t>2026-10-09 14:16:42</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -899,7 +899,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -911,11 +911,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>204388.7</v>
+        <v>204866.56</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-10-08 14:41:25</t>
+          <t>2026-10-09 14:10:30</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -923,7 +923,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>198493.62</v>
+        <v>199200.69</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-10-08 14:31:28</t>
+          <t>2026-10-09 14:18:00</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -947,7 +947,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -959,11 +959,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>9534.139999999999</v>
+        <v>10705.21</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-10-08 14:42:10</t>
+          <t>2026-10-09 14:18:24</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -971,7 +971,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -983,11 +983,11 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>213834</v>
+        <v>213924.52</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-10-08 14:42:53</t>
+          <t>2026-10-09 14:18:05</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -995,7 +995,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -1007,11 +1007,11 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>263077.48</v>
+        <v>263257.05</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-10-08 14:42:14</t>
+          <t>2026-10-09 14:18:35</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -1031,11 +1031,11 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3123.97</v>
+        <v>3736.15</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-10-08 14:42:37</t>
+          <t>2026-10-09 13:56:46</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -1055,11 +1055,11 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>233965.63</v>
+        <v>234455.98</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-10-08 14:41:56</t>
+          <t>2026-10-09 14:16:36</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -1079,11 +1079,11 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>615393.3100000001</v>
+        <v>615877.38</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-10-08 14:42:53</t>
+          <t>2026-10-09 14:18:11</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
@@ -1103,11 +1103,11 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>161296.08</v>
+        <v>161758.72</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-10-08 14:42:41</t>
+          <t>2026-10-09 14:17:17</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
@@ -1127,11 +1127,11 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>43453.25</v>
+        <v>43519.46</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-10-08 14:42:49</t>
+          <t>2026-10-09 14:16:40</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
@@ -1151,11 +1151,11 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>390831.97</v>
+        <v>391831.5</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-10-08 14:40:48</t>
+          <t>2026-10-09 14:17:09</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
@@ -1175,11 +1175,11 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>386924.38</v>
+        <v>387545.72</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-10-08 14:42:36</t>
+          <t>2026-10-09 13:58:27</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
@@ -1199,11 +1199,11 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3835.46</v>
+        <v>4788.27</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-10-08 14:38:51</t>
+          <t>2026-10-09 14:16:48</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
@@ -1223,11 +1223,11 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>234112.85</v>
+        <v>234155.75</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-10-08 14:38:12</t>
+          <t>2026-10-09 14:14:06</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
@@ -1247,11 +1247,11 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>120752.84</v>
+        <v>121905.02</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-10-08 14:40:53</t>
+          <t>2026-10-09 14:18:26</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
@@ -1271,11 +1271,11 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>177469.45</v>
+        <v>177480.71</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-10-08 14:42:45</t>
+          <t>2026-10-09 14:16:15</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
@@ -1295,11 +1295,11 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>162101.17</v>
+        <v>163296.48</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-10-08 14:41:10</t>
+          <t>2026-10-09 14:17:38</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -1319,11 +1319,11 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1532.63</v>
+        <v>2488.8</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-10-08 14:42:44</t>
+          <t>2026-10-09 14:15:27</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
@@ -1343,11 +1343,11 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>106330.22</v>
+        <v>106343.36</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-10-08 14:42:36</t>
+          <t>2026-10-09 14:18:35</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
@@ -1367,11 +1367,11 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>62363.26</v>
+        <v>62435.23</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-10-08 14:38:34</t>
+          <t>2026-10-09 14:13:53</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-10-08 14:40:18</t>
+          <t>2026-10-09 14:15:04</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>227216.94</v>
+        <v>227249.94</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-10-08 14:40:06</t>
+          <t>2026-10-09 14:17:21</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>467388.75</v>
+        <v>467854.91</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-10-08 14:38:00</t>
+          <t>2026-10-09 14:16:47</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -1511,11 +1511,11 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>187177.5</v>
+        <v>187278.62</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-10-08 14:41:58</t>
+          <t>2026-10-09 14:17:28</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
@@ -1535,11 +1535,11 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>373882.86</v>
+        <v>374060.86</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-10-08 14:42:58</t>
+          <t>2026-10-09 14:18:36</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
@@ -1559,11 +1559,11 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>5179.85</v>
+        <v>5227.24</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-10-08 14:40:42</t>
+          <t>2026-10-09 14:14:25</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -1583,11 +1583,11 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3513.08</v>
+        <v>3535.07</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-10-08 14:41:56</t>
+          <t>2026-10-09 14:17:17</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
@@ -1619,7 +1619,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -1631,11 +1631,11 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>553086.1899999999</v>
+        <v>553166.5</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-10-08 14:42:31</t>
+          <t>2026-10-09 14:17:47</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
@@ -1655,11 +1655,11 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>89018.75999999999</v>
+        <v>89996.32000000001</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-10-08 14:42:45</t>
+          <t>2026-10-09 14:04:06</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
@@ -1679,11 +1679,11 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>88886.17999999999</v>
+        <v>89679.28999999999</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-10-08 14:42:29</t>
+          <t>2026-10-09 14:14:20</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
@@ -1703,11 +1703,11 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>316461.91</v>
+        <v>316615.19</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-10-08 14:38:52</t>
+          <t>2026-10-09 14:17:02</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
@@ -1727,11 +1727,11 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>184633.94</v>
+        <v>184686.34</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-10-08 14:42:07</t>
+          <t>2026-10-09 14:17:51</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
@@ -1775,11 +1775,11 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>32436.83</v>
+        <v>33191.73</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-10-08 14:42:37</t>
+          <t>2026-10-09 14:17:55</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
@@ -1799,11 +1799,11 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>197358.07</v>
+        <v>197448.45</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-10-08 14:42:46</t>
+          <t>2026-10-09 14:17:54</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
@@ -1823,11 +1823,11 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>230899.61</v>
+        <v>230958.2</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-10-08 14:38:21</t>
+          <t>2026-10-09 14:17:33</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
@@ -1847,11 +1847,11 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>37802.93</v>
+        <v>38808.74</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-10-08 14:35:44</t>
+          <t>2026-10-09 14:18:36</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
@@ -1871,11 +1871,11 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>40183.66</v>
+        <v>41120.37</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-10-08 14:42:51</t>
+          <t>2026-10-09 14:14:58</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
@@ -1895,11 +1895,11 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>31401.98</v>
+        <v>31402.22</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-10-08 14:40:55</t>
+          <t>2026-10-09 14:15:53</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
@@ -1967,11 +1967,11 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>7613.58</v>
+        <v>8819.82</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-10-08 14:42:59</t>
+          <t>2026-10-09 14:18:40</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
@@ -1995,7 +1995,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-10-08 14:41:42</t>
+          <t>2026-10-09 14:15:14</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
@@ -2015,11 +2015,11 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>25228.63</v>
+        <v>25869.39</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:02</t>
+          <t>2026-10-09 14:15:25</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>25842.97</v>
+        <v>25877.36</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-10-08 14:41:23</t>
+          <t>2026-10-09 14:16:37</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
@@ -2063,11 +2063,11 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>102410.67</v>
+        <v>102526.71</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-10-08 14:42:03</t>
+          <t>2026-10-09 14:18:31</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
@@ -2087,11 +2087,11 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>9085.6</v>
+        <v>9153.77</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-10-08 14:42:33</t>
+          <t>2026-10-09 14:17:29</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
@@ -2111,11 +2111,11 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>136581.64</v>
+        <v>136642.31</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:03</t>
+          <t>2026-10-09 14:14:27</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
@@ -2135,11 +2135,11 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>255992.77</v>
+        <v>256024.33</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-10-08 14:42:35</t>
+          <t>2026-10-09 14:15:36</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
@@ -2159,11 +2159,11 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>237283.27</v>
+        <v>237349.73</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-10-08 14:40:53</t>
+          <t>2026-10-09 14:15:12</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-10-08 14:43:00</t>
+          <t>2026-10-09 14:18:37</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>

--- a/data/kilometrajes_latest.xlsx
+++ b/data/kilometrajes_latest.xlsx
@@ -455,11 +455,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25129.32</v>
+        <v>25130.2</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-09 14:17:52</t>
+          <t>2026-10-10 01:25:21</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -467,7 +467,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -479,11 +479,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>358346.78</v>
+        <v>358398.75</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-09 14:17:55</t>
+          <t>2026-10-09 17:47:31</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -491,7 +491,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -507,7 +507,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-09 14:17:23</t>
+          <t>2026-10-09 23:01:55</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -515,7 +515,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -527,11 +527,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1707903.5</v>
+        <v>1708513.62</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-09 14:14:13</t>
+          <t>2026-10-12 17:04:53</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -539,7 +539,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -551,11 +551,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>144275</v>
+        <v>144356.42</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-09 14:16:19</t>
+          <t>2026-10-12 17:04:27</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -563,7 +563,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -575,11 +575,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>190548.59</v>
+        <v>190615.08</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-09 14:15:19</t>
+          <t>2026-10-12 17:01:59</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -587,7 +587,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -599,11 +599,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>788261.6899999999</v>
+        <v>789910.12</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:20</t>
+          <t>2026-10-12 11:55:48</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -611,7 +611,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -623,11 +623,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1345253.38</v>
+        <v>1345254.38</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-09 14:17:51</t>
+          <t>2026-10-12 17:02:18</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -635,7 +635,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -651,7 +651,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-09 14:16:35</t>
+          <t>2026-10-12 17:04:22</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -659,7 +659,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -671,11 +671,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1253042.12</v>
+        <v>1254228.75</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-09 14:16:07</t>
+          <t>2026-10-10 16:31:45</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -683,7 +683,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -695,11 +695,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>126895.13</v>
+        <v>126940.9</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-09 14:17:36</t>
+          <t>2026-10-12 17:02:38</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -707,7 +707,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -719,11 +719,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>357324</v>
+        <v>358243.19</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:26</t>
+          <t>2026-10-10 19:19:11</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -743,11 +743,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>199372.08</v>
+        <v>200587.5</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:26</t>
+          <t>2026-10-11 20:25:29</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -755,7 +755,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -767,11 +767,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>288619.91</v>
+        <v>288647.84</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:20</t>
+          <t>2026-10-12 17:02:03</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -791,11 +791,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>237661.25</v>
+        <v>238572.02</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-09 14:17:24</t>
+          <t>2026-10-11 12:48:18</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -803,7 +803,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -815,11 +815,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>594369.41</v>
+        <v>595596.34</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-10-09 14:17:33</t>
+          <t>2026-10-10 16:36:30</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -827,7 +827,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -839,11 +839,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>303012.22</v>
+        <v>303177.84</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-09 14:17:27</t>
+          <t>2026-10-11 17:06:55</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -851,7 +851,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -863,11 +863,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>20290.07</v>
+        <v>21480.4</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-10-09 14:17:51</t>
+          <t>2026-10-10 20:43:28</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -875,7 +875,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -887,11 +887,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>98390.82000000001</v>
+        <v>98443.14999999999</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-10-09 14:16:42</t>
+          <t>2026-10-12 16:58:22</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -899,7 +899,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -911,11 +911,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>204866.56</v>
+        <v>206498.47</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-10-09 14:10:30</t>
+          <t>2026-10-12 08:01:55</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -923,7 +923,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>199200.69</v>
+        <v>199874.33</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:00</t>
+          <t>2026-10-11 00:05:04</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -947,7 +947,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -959,11 +959,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10705.21</v>
+        <v>11883.66</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:24</t>
+          <t>2026-10-11 03:46:58</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -971,7 +971,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -983,11 +983,11 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>213924.52</v>
+        <v>214002.3</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:05</t>
+          <t>2026-10-12 17:06:29</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -995,7 +995,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -1007,11 +1007,11 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>263257.05</v>
+        <v>263295.67</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:35</t>
+          <t>2026-10-12 17:04:06</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -1031,11 +1031,11 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3736.15</v>
+        <v>4843.24</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-10-09 13:56:46</t>
+          <t>2026-10-10 17:46:16</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -1055,11 +1055,11 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>234455.98</v>
+        <v>234763.12</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-10-09 14:16:36</t>
+          <t>2026-10-12 17:03:46</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -1079,11 +1079,11 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>615877.38</v>
+        <v>617526.62</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:11</t>
+          <t>2026-10-12 17:05:23</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
@@ -1103,11 +1103,11 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>161758.72</v>
+        <v>162891.67</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-10-09 14:17:17</t>
+          <t>2026-10-12 17:02:23</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
@@ -1127,11 +1127,11 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>43519.46</v>
+        <v>43540.17</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-10-09 14:16:40</t>
+          <t>2026-10-12 17:03:02</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
@@ -1151,11 +1151,11 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>391831.5</v>
+        <v>392361.81</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-10-09 14:17:09</t>
+          <t>2026-10-10 20:37:58</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
@@ -1175,11 +1175,11 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>387545.72</v>
+        <v>388662.12</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-10-09 13:58:27</t>
+          <t>2026-10-12 17:05:58</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
@@ -1199,11 +1199,11 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4788.27</v>
+        <v>4847.4</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-10-09 14:16:48</t>
+          <t>2026-10-12 17:06:00</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
@@ -1223,11 +1223,11 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>234155.75</v>
+        <v>234155.99</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-10-09 14:14:06</t>
+          <t>2026-10-12 17:03:31</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
@@ -1247,11 +1247,11 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>121905.02</v>
+        <v>122527.87</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:26</t>
+          <t>2026-10-12 17:05:43</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
@@ -1271,11 +1271,11 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>177480.71</v>
+        <v>178730.73</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-10-09 14:16:15</t>
+          <t>2026-10-12 17:03:30</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
@@ -1295,11 +1295,11 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>163296.48</v>
+        <v>163302.56</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-10-09 14:17:38</t>
+          <t>2026-10-12 17:02:09</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -1319,11 +1319,11 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2488.8</v>
+        <v>2549.1</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-10-09 14:15:27</t>
+          <t>2026-10-12 17:04:52</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
@@ -1343,11 +1343,11 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>106343.36</v>
+        <v>106357.26</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:35</t>
+          <t>2026-10-12 17:04:47</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
@@ -1367,11 +1367,11 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>62435.23</v>
+        <v>62522.43</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-10-09 14:13:53</t>
+          <t>2026-10-12 17:06:09</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-10-09 14:15:04</t>
+          <t>2026-10-12 17:04:52</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>227249.94</v>
+        <v>227255.38</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-10-09 14:17:21</t>
+          <t>2026-10-12 17:06:15</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>467854.91</v>
+        <v>468057.62</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-10-09 14:16:47</t>
+          <t>2026-10-12 17:00:44</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -1511,11 +1511,11 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>187278.62</v>
+        <v>187332.41</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-10-09 14:17:28</t>
+          <t>2026-10-12 17:02:23</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
@@ -1535,11 +1535,11 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>374060.86</v>
+        <v>374066.86</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:36</t>
+          <t>2026-10-12 17:04:31</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
@@ -1559,11 +1559,11 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>5227.24</v>
+        <v>5269.73</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-10-09 14:14:25</t>
+          <t>2026-10-12 17:04:32</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-10-09 14:17:17</t>
+          <t>2026-10-12 17:04:42</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
@@ -1619,7 +1619,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -1631,11 +1631,11 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>553166.5</v>
+        <v>553230.12</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-10-09 14:17:47</t>
+          <t>2026-10-12 17:06:44</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
@@ -1655,11 +1655,11 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>89996.32000000001</v>
+        <v>91341.57000000001</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-10-09 14:04:06</t>
+          <t>2026-10-12 17:02:04</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
@@ -1679,11 +1679,11 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>89679.28999999999</v>
+        <v>90657</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-10-09 14:14:20</t>
+          <t>2026-10-12 17:06:54</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
@@ -1703,11 +1703,11 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>316615.19</v>
+        <v>316677.47</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-10-09 14:17:02</t>
+          <t>2026-10-12 17:03:51</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
@@ -1727,11 +1727,11 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>184686.34</v>
+        <v>184749.17</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-10-09 14:17:51</t>
+          <t>2026-10-12 17:03:40</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
@@ -1775,11 +1775,11 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>33191.73</v>
+        <v>34804.47</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-10-09 14:17:55</t>
+          <t>2026-10-12 17:03:20</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
@@ -1799,11 +1799,11 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>197448.45</v>
+        <v>197519.01</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-10-09 14:17:54</t>
+          <t>2026-10-12 17:06:06</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
@@ -1823,11 +1823,11 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>230958.2</v>
+        <v>231021.41</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-10-09 14:17:33</t>
+          <t>2026-10-12 17:06:45</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
@@ -1847,11 +1847,11 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>38808.74</v>
+        <v>38869.52</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:36</t>
+          <t>2026-10-12 17:06:14</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
@@ -1871,11 +1871,11 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>41120.37</v>
+        <v>41175.6</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-10-09 14:14:58</t>
+          <t>2026-10-10 05:25:46</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
@@ -1895,11 +1895,11 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>31402.22</v>
+        <v>31402.45</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-10-09 14:15:53</t>
+          <t>2026-10-12 17:06:07</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
@@ -1967,11 +1967,11 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>8819.82</v>
+        <v>10034.96</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:40</t>
+          <t>2026-10-12 17:04:35</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
@@ -1995,7 +1995,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-10-09 14:15:14</t>
+          <t>2026-10-12 17:05:24</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
@@ -2015,11 +2015,11 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>25869.39</v>
+        <v>26965.9</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-10-09 14:15:25</t>
+          <t>2026-10-12 17:05:42</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>25877.36</v>
+        <v>25900.66</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-10-09 14:16:37</t>
+          <t>2026-10-12 17:03:06</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
@@ -2063,11 +2063,11 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>102526.71</v>
+        <v>102634.54</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:31</t>
+          <t>2026-10-12 17:06:29</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
@@ -2087,11 +2087,11 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>9153.77</v>
+        <v>9202.639999999999</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-10-09 14:17:29</t>
+          <t>2026-10-12 17:01:26</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
@@ -2111,11 +2111,11 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>136642.31</v>
+        <v>136691.91</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-10-09 14:14:27</t>
+          <t>2026-10-12 16:53:46</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-10-09 14:15:36</t>
+          <t>2026-10-12 17:05:08</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
@@ -2159,11 +2159,11 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>237349.73</v>
+        <v>237367.41</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-10-09 14:15:12</t>
+          <t>2026-10-12 17:05:44</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-10-09 14:18:37</t>
+          <t>2026-10-12 17:06:57</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>

--- a/data/kilometrajes_latest.xlsx
+++ b/data/kilometrajes_latest.xlsx
@@ -455,11 +455,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25130.2</v>
+        <v>25835.63</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-10 01:25:21</t>
+          <t>2026-10-13 14:55:24</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -467,7 +467,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -479,11 +479,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>358398.75</v>
+        <v>358505.03</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-09 17:47:31</t>
+          <t>2026-10-13 14:52:32</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -491,7 +491,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -527,11 +527,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1708513.62</v>
+        <v>1709223.5</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-12 17:04:53</t>
+          <t>2026-10-13 14:56:01</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -539,7 +539,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -551,11 +551,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>144356.42</v>
+        <v>144444.71</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-12 17:04:27</t>
+          <t>2026-10-13 14:55:44</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -563,7 +563,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -575,11 +575,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>190615.08</v>
+        <v>190678.95</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-12 17:01:59</t>
+          <t>2026-10-13 14:52:38</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -587,7 +587,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -599,11 +599,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>789910.12</v>
+        <v>789965.62</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-12 11:55:48</t>
+          <t>2026-10-13 14:56:05</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -611,7 +611,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -623,11 +623,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1345254.38</v>
+        <v>1345967.88</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-12 17:02:18</t>
+          <t>2026-10-13 14:54:09</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -635,7 +635,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -647,11 +647,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>179669.59</v>
+        <v>179691.27</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-12 17:04:22</t>
+          <t>2026-10-13 14:55:18</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -659,7 +659,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -671,11 +671,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1254228.75</v>
+        <v>1254421.38</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-10 16:31:45</t>
+          <t>2026-10-13 14:54:58</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -683,7 +683,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -695,11 +695,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>126940.9</v>
+        <v>127005.46</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-12 17:02:38</t>
+          <t>2026-10-13 14:54:13</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -707,7 +707,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -719,11 +719,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>358243.19</v>
+        <v>358283.25</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-10 19:19:11</t>
+          <t>2026-10-13 14:55:39</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -747,7 +747,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-10-11 20:25:29</t>
+          <t>2026-10-13 13:32:23</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -755,7 +755,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -767,11 +767,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>288647.84</v>
+        <v>288896.69</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-10-12 17:02:03</t>
+          <t>2026-10-13 14:54:30</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -791,11 +791,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>238572.02</v>
+        <v>238610.88</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-11 12:48:18</t>
+          <t>2026-10-13 14:55:28</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -803,7 +803,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-10-10 16:36:30</t>
+          <t>2026-10-13 14:53:49</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -827,7 +827,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -839,11 +839,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>303177.84</v>
+        <v>303644.97</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-11 17:06:55</t>
+          <t>2026-10-13 14:55:54</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -851,7 +851,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -863,11 +863,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>21480.4</v>
+        <v>21480.84</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-10-10 20:43:28</t>
+          <t>2026-10-13 14:54:39</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -875,7 +875,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -887,11 +887,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>98443.14999999999</v>
+        <v>98493.99000000001</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-10-12 16:58:22</t>
+          <t>2026-10-13 14:55:08</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -899,7 +899,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -911,11 +911,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>206498.47</v>
+        <v>206498.53</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-10-12 08:01:55</t>
+          <t>2026-10-13 14:52:41</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -923,7 +923,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>199874.33</v>
+        <v>199874.48</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-10-11 00:05:04</t>
+          <t>2026-10-13 14:52:37</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -947,7 +947,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -963,7 +963,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-10-11 03:46:58</t>
+          <t>2026-10-13 14:52:56</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -971,7 +971,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -983,11 +983,11 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>214002.3</v>
+        <v>214049.16</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:29</t>
+          <t>2026-10-13 14:56:01</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -995,7 +995,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -1007,11 +1007,11 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>263295.67</v>
+        <v>263489.77</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-10-12 17:04:06</t>
+          <t>2026-10-13 14:55:31</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-10-10 17:46:16</t>
+          <t>2026-10-13 11:01:19</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -1055,11 +1055,11 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>234763.12</v>
+        <v>235057.3</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-10-12 17:03:46</t>
+          <t>2026-10-13 14:55:44</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -1079,11 +1079,11 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>617526.62</v>
+        <v>617526.8100000001</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-10-12 17:05:23</t>
+          <t>2026-10-13 14:55:13</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
@@ -1103,11 +1103,11 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>162891.67</v>
+        <v>163004.45</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-10-12 17:02:23</t>
+          <t>2026-10-13 14:55:53</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
@@ -1127,11 +1127,11 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>43540.17</v>
+        <v>43627.46</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-10-12 17:03:02</t>
+          <t>2026-10-13 14:54:57</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
@@ -1151,11 +1151,11 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>392361.81</v>
+        <v>392361.91</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-10-10 20:37:58</t>
+          <t>2026-10-13 14:55:58</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-10-12 17:05:58</t>
+          <t>2026-10-13 14:55:38</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
@@ -1199,11 +1199,11 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4847.4</v>
+        <v>6207.99</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:00</t>
+          <t>2026-10-13 14:56:08</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-10-12 17:03:31</t>
+          <t>2026-10-13 14:52:11</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
@@ -1247,11 +1247,11 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>122527.87</v>
+        <v>123129.21</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-10-12 17:05:43</t>
+          <t>2026-10-13 14:56:07</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-10-12 17:03:30</t>
+          <t>2026-10-13 14:52:21</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
@@ -1295,11 +1295,11 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>163302.56</v>
+        <v>164053.12</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-10-12 17:02:09</t>
+          <t>2026-10-13 14:56:01</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -1319,11 +1319,11 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2549.1</v>
+        <v>3926.82</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-10-12 17:04:52</t>
+          <t>2026-10-13 14:52:41</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
@@ -1343,11 +1343,11 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>106357.26</v>
+        <v>106369.95</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-10-12 17:04:47</t>
+          <t>2026-10-13 14:55:58</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
@@ -1367,11 +1367,11 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>62522.43</v>
+        <v>62567.59</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:09</t>
+          <t>2026-10-13 14:52:36</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-10-12 17:04:52</t>
+          <t>2026-10-13 14:54:15</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>227255.38</v>
+        <v>227256.3</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:15</t>
+          <t>2026-10-13 14:55:38</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>468057.62</v>
+        <v>468100.94</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-10-12 17:00:44</t>
+          <t>2026-10-13 14:54:21</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -1511,11 +1511,11 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>187332.41</v>
+        <v>187364.67</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-10-12 17:02:23</t>
+          <t>2026-10-13 14:54:53</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
@@ -1535,11 +1535,11 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>374066.86</v>
+        <v>374171.61</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-10-12 17:04:31</t>
+          <t>2026-10-13 14:53:46</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
@@ -1559,11 +1559,11 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>5269.73</v>
+        <v>5297.08</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-10-12 17:04:32</t>
+          <t>2026-10-13 14:51:54</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-10-12 17:04:42</t>
+          <t>2026-10-13 14:51:51</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
@@ -1619,7 +1619,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:44</t>
+          <t>2026-10-13 14:53:44</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
@@ -1655,11 +1655,11 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>91341.57000000001</v>
+        <v>91538.63</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-10-12 17:02:04</t>
+          <t>2026-10-13 14:54:11</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
@@ -1679,11 +1679,11 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>90657</v>
+        <v>91112.32000000001</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:54</t>
+          <t>2026-10-13 14:54:45</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
@@ -1703,11 +1703,11 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>316677.47</v>
+        <v>316840</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-10-12 17:03:51</t>
+          <t>2026-10-13 14:56:05</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
@@ -1727,11 +1727,11 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>184749.17</v>
+        <v>184796.28</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-10-12 17:03:40</t>
+          <t>2026-10-13 14:55:59</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
@@ -1775,11 +1775,11 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>34804.47</v>
+        <v>34858.55</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-10-12 17:03:20</t>
+          <t>2026-10-13 14:53:41</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
@@ -1799,11 +1799,11 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>197519.01</v>
+        <v>197562.46</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:06</t>
+          <t>2026-10-13 14:55:32</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
@@ -1823,11 +1823,11 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>231021.41</v>
+        <v>231102.69</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:45</t>
+          <t>2026-10-13 14:55:25</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
@@ -1847,11 +1847,11 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>38869.52</v>
+        <v>40247.45</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:14</t>
+          <t>2026-10-13 14:54:55</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
@@ -1895,11 +1895,11 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>31402.45</v>
+        <v>31402.57</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:07</t>
+          <t>2026-10-13 14:51:20</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
@@ -1967,11 +1967,11 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>10034.96</v>
+        <v>10035.11</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-10-12 17:04:35</t>
+          <t>2026-10-13 14:55:24</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
@@ -1995,7 +1995,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-10-12 17:05:24</t>
+          <t>2026-10-13 14:55:52</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
@@ -2015,11 +2015,11 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>26965.9</v>
+        <v>26966.27</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-10-12 17:05:42</t>
+          <t>2026-10-13 14:53:16</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>25900.66</v>
+        <v>25913.69</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-10-12 17:03:06</t>
+          <t>2026-10-13 14:53:07</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
@@ -2063,11 +2063,11 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>102634.54</v>
+        <v>102737.23</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:29</t>
+          <t>2026-10-13 14:55:29</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
@@ -2087,11 +2087,11 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>9202.639999999999</v>
+        <v>9278.73</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-10-12 17:01:26</t>
+          <t>2026-10-13 14:54:42</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
@@ -2111,11 +2111,11 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>136691.91</v>
+        <v>136716.08</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-10-12 16:53:46</t>
+          <t>2026-10-13 14:56:12</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-10-12 17:05:08</t>
+          <t>2026-10-13 14:52:16</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
@@ -2159,11 +2159,11 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>237367.41</v>
+        <v>237517.16</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-10-12 17:05:44</t>
+          <t>2026-10-13 14:54:42</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-10-12 17:06:57</t>
+          <t>2026-10-13 14:56:19</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>

--- a/data/kilometrajes_latest.xlsx
+++ b/data/kilometrajes_latest.xlsx
@@ -455,11 +455,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25835.63</v>
+        <v>26408.79</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:55:24</t>
+          <t>2026-10-14 12:40:33</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -467,7 +467,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -479,11 +479,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>358505.03</v>
+        <v>358569.69</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-13 14:52:32</t>
+          <t>2026-10-14 12:41:30</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -491,7 +491,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -503,11 +503,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>221664.94</v>
+        <v>222487.14</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-09 23:01:55</t>
+          <t>2026-10-14 12:39:33</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -515,7 +515,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -527,11 +527,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1709223.5</v>
+        <v>1710373.75</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:01</t>
+          <t>2026-10-14 12:41:28</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -539,7 +539,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -551,11 +551,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>144444.71</v>
+        <v>144506.29</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-13 14:55:44</t>
+          <t>2026-10-14 12:41:44</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -563,7 +563,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -575,11 +575,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>190678.95</v>
+        <v>190712.83</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-13 14:52:38</t>
+          <t>2026-10-14 12:41:54</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -587,7 +587,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -603,7 +603,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:05</t>
+          <t>2026-10-14 12:39:55</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -611,7 +611,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -623,11 +623,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1345967.88</v>
+        <v>1346546.5</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-13 14:54:09</t>
+          <t>2026-10-14 12:40:23</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -635,7 +635,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -647,11 +647,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>179691.27</v>
+        <v>179742.43</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-13 14:55:18</t>
+          <t>2026-10-14 12:41:12</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -659,7 +659,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -671,11 +671,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1254421.38</v>
+        <v>1255261.38</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-13 14:54:58</t>
+          <t>2026-10-14 12:39:47</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -683,7 +683,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -695,11 +695,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>127005.46</v>
+        <v>127053.58</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-13 14:54:13</t>
+          <t>2026-10-14 12:41:59</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -707,7 +707,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -719,11 +719,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>358283.25</v>
+        <v>359424.91</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-13 14:55:39</t>
+          <t>2026-10-14 12:41:20</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -743,11 +743,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>200587.5</v>
+        <v>200598.72</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-10-13 13:32:23</t>
+          <t>2026-10-14 12:41:54</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -755,7 +755,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -767,11 +767,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>288896.69</v>
+        <v>288961.22</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-10-13 14:54:30</t>
+          <t>2026-10-14 12:40:57</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -791,11 +791,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>238610.88</v>
+        <v>239742.94</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-13 14:55:28</t>
+          <t>2026-10-14 12:41:51</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -803,7 +803,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -815,11 +815,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>595596.34</v>
+        <v>595609.97</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-10-13 14:53:49</t>
+          <t>2026-10-14 12:40:57</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -827,7 +827,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -839,11 +839,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>303644.97</v>
+        <v>304145.97</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-13 14:55:54</t>
+          <t>2026-10-14 12:41:30</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -851,7 +851,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -863,11 +863,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>21480.84</v>
+        <v>21494.21</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-10-13 14:54:39</t>
+          <t>2026-10-14 12:39:54</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -875,7 +875,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -887,11 +887,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>98493.99000000001</v>
+        <v>98541.78</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-10-13 14:55:08</t>
+          <t>2026-10-14 12:41:54</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -899,7 +899,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -911,11 +911,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>206498.53</v>
+        <v>207638.55</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-10-13 14:52:41</t>
+          <t>2026-10-14 12:41:51</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -923,7 +923,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>199874.48</v>
+        <v>200335.61</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-10-13 14:52:37</t>
+          <t>2026-10-14 12:37:22</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -947,7 +947,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -959,11 +959,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>11883.66</v>
+        <v>11895.99</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-10-13 14:52:56</t>
+          <t>2026-10-14 12:38:48</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -971,7 +971,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -983,11 +983,11 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>214049.16</v>
+        <v>214121.61</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:01</t>
+          <t>2026-10-14 12:40:55</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -995,7 +995,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -1007,11 +1007,11 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>263489.77</v>
+        <v>263527.83</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-10-13 14:55:31</t>
+          <t>2026-10-14 12:40:17</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -1031,11 +1031,11 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4843.24</v>
+        <v>5551.12</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-10-13 11:01:19</t>
+          <t>2026-10-14 12:36:25</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -1055,11 +1055,11 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>235057.3</v>
+        <v>235605.35</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-10-13 14:55:44</t>
+          <t>2026-10-14 12:40:15</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -1079,11 +1079,11 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>617526.8100000001</v>
+        <v>618689.25</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-10-13 14:55:13</t>
+          <t>2026-10-14 12:38:21</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
@@ -1103,11 +1103,11 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>163004.45</v>
+        <v>163917.47</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-10-13 14:55:53</t>
+          <t>2026-10-14 12:41:56</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
@@ -1127,11 +1127,11 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>43627.46</v>
+        <v>43963.28</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-10-13 14:54:57</t>
+          <t>2026-10-14 12:41:22</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
@@ -1151,11 +1151,11 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>392361.91</v>
+        <v>393537.34</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-10-13 14:55:58</t>
+          <t>2026-10-14 12:41:56</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
@@ -1175,11 +1175,11 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>388662.12</v>
+        <v>389377.19</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-10-13 14:55:38</t>
+          <t>2026-10-14 12:38:38</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
@@ -1199,11 +1199,11 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>6207.99</v>
+        <v>6686.27</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:08</t>
+          <t>2026-10-14 12:40:10</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-10-13 14:52:11</t>
+          <t>2026-10-14 12:39:11</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
@@ -1247,11 +1247,11 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>123129.21</v>
+        <v>123921.4</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:07</t>
+          <t>2026-10-14 12:39:31</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
@@ -1271,11 +1271,11 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>178730.73</v>
+        <v>178743.96</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-10-13 14:52:21</t>
+          <t>2026-10-14 12:37:47</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
@@ -1295,11 +1295,11 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>164053.12</v>
+        <v>164543.67</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:01</t>
+          <t>2026-10-14 12:41:44</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -1319,11 +1319,11 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3926.82</v>
+        <v>4410.42</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-10-13 14:52:41</t>
+          <t>2026-10-14 12:39:53</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
@@ -1343,11 +1343,11 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>106369.95</v>
+        <v>106388.34</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-10-13 14:55:58</t>
+          <t>2026-10-14 12:40:29</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
@@ -1367,11 +1367,11 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>62567.59</v>
+        <v>62610.66</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-10-13 14:52:36</t>
+          <t>2026-10-14 12:41:20</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-10-13 14:54:15</t>
+          <t>2026-10-14 12:38:52</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-10-13 14:55:38</t>
+          <t>2026-10-14 12:36:41</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>468100.94</v>
+        <v>468131.69</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-10-13 14:54:21</t>
+          <t>2026-10-14 12:38:01</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -1511,11 +1511,11 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>187364.67</v>
+        <v>187401.95</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-10-13 14:54:53</t>
+          <t>2026-10-14 12:41:16</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
@@ -1535,11 +1535,11 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>374171.61</v>
+        <v>374259.3</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-10-13 14:53:46</t>
+          <t>2026-10-14 12:42:07</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
@@ -1559,11 +1559,11 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>5297.08</v>
+        <v>5346.43</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-10-13 14:51:54</t>
+          <t>2026-10-14 12:41:26</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-10-13 14:51:51</t>
+          <t>2026-10-14 12:39:32</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
@@ -1619,7 +1619,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -1631,11 +1631,11 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>553230.12</v>
+        <v>553265.9399999999</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-10-13 14:53:44</t>
+          <t>2026-10-14 12:42:08</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-10-13 14:54:11</t>
+          <t>2026-10-14 12:38:45</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
@@ -1679,11 +1679,11 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>91112.32000000001</v>
+        <v>91563.63</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-10-13 14:54:45</t>
+          <t>2026-10-14 12:40:49</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
@@ -1703,11 +1703,11 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>316840</v>
+        <v>317030.16</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:05</t>
+          <t>2026-10-14 12:41:27</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
@@ -1727,11 +1727,11 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>184796.28</v>
+        <v>184839.78</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-10-13 14:55:59</t>
+          <t>2026-10-14 12:33:58</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-10-13 14:53:41</t>
+          <t>2026-10-13 21:16:58</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
@@ -1799,11 +1799,11 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>197562.46</v>
+        <v>197633.45</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-10-13 14:55:32</t>
+          <t>2026-10-14 12:41:19</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
@@ -1823,11 +1823,11 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>231102.69</v>
+        <v>231203.62</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-10-13 14:55:25</t>
+          <t>2026-10-14 12:42:09</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
@@ -1847,11 +1847,11 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>40247.45</v>
+        <v>40247.89</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-10-13 14:54:55</t>
+          <t>2026-10-14 12:41:27</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
@@ -1895,11 +1895,11 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>31402.57</v>
+        <v>31402.79</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-10-13 14:51:20</t>
+          <t>2026-10-14 12:37:54</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
@@ -1967,11 +1967,11 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>10035.11</v>
+        <v>10044.76</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-10-13 14:55:24</t>
+          <t>2026-10-14 12:41:23</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
@@ -1991,11 +1991,11 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>25651.5</v>
+        <v>25652.31</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-10-13 14:55:52</t>
+          <t>2026-10-14 12:42:05</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
@@ -2015,11 +2015,11 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>26966.27</v>
+        <v>26979.38</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-10-13 14:53:16</t>
+          <t>2026-10-14 12:41:08</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>25913.69</v>
+        <v>25967.83</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-10-13 14:53:07</t>
+          <t>2026-10-14 12:42:04</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
@@ -2063,11 +2063,11 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>102737.23</v>
+        <v>102895.96</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-10-13 14:55:29</t>
+          <t>2026-10-14 12:38:51</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
@@ -2087,11 +2087,11 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>9278.73</v>
+        <v>9347.77</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-10-13 14:54:42</t>
+          <t>2026-10-14 12:40:53</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
@@ -2111,11 +2111,11 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>136716.08</v>
+        <v>136792.42</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:12</t>
+          <t>2026-10-14 12:37:43</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
@@ -2135,11 +2135,11 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>256024.33</v>
+        <v>256072.92</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-10-13 14:52:16</t>
+          <t>2026-10-14 12:40:48</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
@@ -2159,11 +2159,11 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>237517.16</v>
+        <v>237611.17</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-10-13 14:54:42</t>
+          <t>2026-10-14 12:41:43</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-10-13 14:56:19</t>
+          <t>2026-10-14 12:42:27</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>

--- a/data/kilometrajes_latest.xlsx
+++ b/data/kilometrajes_latest.xlsx
@@ -455,11 +455,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26408.79</v>
+        <v>27018.36</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-14 12:40:33</t>
+          <t>2026-10-15 12:27:20</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -467,7 +467,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -479,11 +479,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>358569.69</v>
+        <v>358676.66</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-14 12:41:30</t>
+          <t>2026-10-15 12:26:53</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -491,7 +491,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -503,11 +503,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>222487.14</v>
+        <v>223022.72</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-14 12:39:33</t>
+          <t>2026-10-15 12:27:35</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -515,7 +515,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -527,11 +527,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1710373.75</v>
+        <v>1711237.88</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-14 12:41:28</t>
+          <t>2026-10-15 12:28:59</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -539,7 +539,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -551,11 +551,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>144506.29</v>
+        <v>144583.2</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-14 12:41:44</t>
+          <t>2026-10-15 12:28:03</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -563,7 +563,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -575,11 +575,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>190712.83</v>
+        <v>190799.89</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-14 12:41:54</t>
+          <t>2026-10-15 12:28:19</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -587,7 +587,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -599,11 +599,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>789965.62</v>
+        <v>791044.0600000001</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-14 12:39:55</t>
+          <t>2026-10-15 12:26:13</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -611,7 +611,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -623,11 +623,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1346546.5</v>
+        <v>1347162</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-14 12:40:23</t>
+          <t>2026-10-15 12:26:00</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -635,7 +635,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -647,11 +647,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>179742.43</v>
+        <v>179779.16</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-14 12:41:12</t>
+          <t>2026-10-15 12:21:45</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -659,7 +659,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -671,11 +671,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1255261.38</v>
+        <v>1255796.75</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-14 12:39:47</t>
+          <t>2026-10-15 12:25:30</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -683,7 +683,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -695,11 +695,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>127053.58</v>
+        <v>127232</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-14 12:41:59</t>
+          <t>2026-10-15 12:18:20</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -707,7 +707,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -719,11 +719,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>359424.91</v>
+        <v>360636.28</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-14 12:41:20</t>
+          <t>2026-10-15 12:29:16</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -743,11 +743,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>200598.72</v>
+        <v>201770.25</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-10-14 12:41:54</t>
+          <t>2026-10-15 12:27:48</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -755,7 +755,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -767,11 +767,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>288961.22</v>
+        <v>289063.88</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-10-14 12:40:57</t>
+          <t>2026-10-15 12:29:25</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -791,11 +791,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>239742.94</v>
+        <v>240941.14</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-14 12:41:51</t>
+          <t>2026-10-15 12:26:52</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -803,7 +803,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -815,11 +815,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>595609.97</v>
+        <v>596796.59</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-10-14 12:40:57</t>
+          <t>2026-10-15 12:29:27</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -827,7 +827,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -839,11 +839,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>304145.97</v>
+        <v>305353</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-14 12:41:30</t>
+          <t>2026-10-15 12:26:29</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -851,7 +851,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -863,11 +863,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>21494.21</v>
+        <v>22674.61</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-10-14 12:39:54</t>
+          <t>2026-10-15 12:27:35</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -875,7 +875,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -887,11 +887,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>98541.78</v>
+        <v>98659.88</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-10-14 12:41:54</t>
+          <t>2026-10-15 12:28:05</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -899,7 +899,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -911,11 +911,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>207638.55</v>
+        <v>208151.52</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-10-14 12:41:51</t>
+          <t>2026-10-15 12:29:25</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -923,7 +923,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>200335.61</v>
+        <v>200342.11</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-10-14 12:37:22</t>
+          <t>2026-10-15 12:23:32</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -947,7 +947,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -959,11 +959,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>11895.99</v>
+        <v>13063.5</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-10-14 12:38:48</t>
+          <t>2026-10-15 12:22:00</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -971,7 +971,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -983,11 +983,11 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>214121.61</v>
+        <v>214192.89</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-10-14 12:40:55</t>
+          <t>2026-10-15 12:28:08</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -995,7 +995,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -1007,11 +1007,11 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>263527.83</v>
+        <v>263697.23</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-10-14 12:40:17</t>
+          <t>2026-10-15 12:27:10</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -1031,11 +1031,11 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5551.12</v>
+        <v>5999.95</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-10-14 12:36:25</t>
+          <t>2026-10-15 12:27:12</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -1055,11 +1055,11 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>235605.35</v>
+        <v>235942.26</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-10-14 12:40:15</t>
+          <t>2026-10-15 12:26:52</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -1079,11 +1079,11 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>618689.25</v>
+        <v>619221.3100000001</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-10-14 12:38:21</t>
+          <t>2026-10-15 12:27:07</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
@@ -1103,11 +1103,11 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>163917.47</v>
+        <v>164195.23</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-10-14 12:41:56</t>
+          <t>2026-10-15 12:27:51</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
@@ -1127,11 +1127,11 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>43963.28</v>
+        <v>44551.93</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-10-14 12:41:22</t>
+          <t>2026-10-15 12:28:25</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
@@ -1151,11 +1151,11 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>393537.34</v>
+        <v>394813.72</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-10-14 12:41:56</t>
+          <t>2026-10-15 12:27:14</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
@@ -1175,11 +1175,11 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>389377.19</v>
+        <v>389831.06</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-10-14 12:38:38</t>
+          <t>2026-10-15 12:27:17</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
@@ -1199,11 +1199,11 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>6686.27</v>
+        <v>7642.05</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-10-14 12:40:10</t>
+          <t>2026-10-15 12:26:24</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-10-14 12:39:11</t>
+          <t>2026-10-15 12:28:24</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
@@ -1247,11 +1247,11 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>123921.4</v>
+        <v>125005.98</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-10-14 12:39:31</t>
+          <t>2026-10-15 12:27:56</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
@@ -1271,11 +1271,11 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>178743.96</v>
+        <v>178974.57</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-10-14 12:37:47</t>
+          <t>2026-10-15 12:28:58</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
@@ -1295,11 +1295,11 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>164543.67</v>
+        <v>165663.38</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-10-14 12:41:44</t>
+          <t>2026-10-15 12:29:12</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -1319,11 +1319,11 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4410.42</v>
+        <v>5378.04</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-10-14 12:39:53</t>
+          <t>2026-10-15 12:23:30</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
@@ -1343,11 +1343,11 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>106388.34</v>
+        <v>106400.66</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-10-14 12:40:29</t>
+          <t>2026-10-15 12:25:37</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
@@ -1367,11 +1367,11 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>62610.66</v>
+        <v>62665.29</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-10-14 12:41:20</t>
+          <t>2026-10-15 12:28:57</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-10-14 12:38:52</t>
+          <t>2026-10-15 12:28:09</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-10-14 12:36:41</t>
+          <t>2026-10-15 12:28:24</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>468131.69</v>
+        <v>468524.69</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-10-14 12:38:01</t>
+          <t>2026-10-15 12:26:42</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -1511,11 +1511,11 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>187401.95</v>
+        <v>187469.94</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-10-14 12:41:16</t>
+          <t>2026-10-15 12:28:09</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
@@ -1535,11 +1535,11 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>374259.3</v>
+        <v>374397.14</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:07</t>
+          <t>2026-10-15 12:26:17</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
@@ -1559,11 +1559,11 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>5346.43</v>
+        <v>5413.41</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-10-14 12:41:26</t>
+          <t>2026-10-15 12:29:25</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-10-14 12:39:32</t>
+          <t>2026-10-15 12:21:49</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
@@ -1619,7 +1619,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -1631,11 +1631,11 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>553265.9399999999</v>
+        <v>553375.4399999999</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:08</t>
+          <t>2026-10-15 12:24:08</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
@@ -1655,11 +1655,11 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>91538.63</v>
+        <v>92470.59</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-10-14 12:38:45</t>
+          <t>2026-10-15 12:27:06</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
@@ -1679,11 +1679,11 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>91563.63</v>
+        <v>91630.61</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-10-14 12:40:49</t>
+          <t>2026-10-15 12:27:34</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
@@ -1703,11 +1703,11 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>317030.16</v>
+        <v>317157.75</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-10-14 12:41:27</t>
+          <t>2026-10-15 12:23:37</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
@@ -1727,11 +1727,11 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>184839.78</v>
+        <v>184887.58</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-10-14 12:33:58</t>
+          <t>2026-10-15 12:29:13</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
@@ -1775,11 +1775,11 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>34858.55</v>
+        <v>35923.33</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-10-13 21:16:58</t>
+          <t>2026-10-15 12:26:32</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
@@ -1799,11 +1799,11 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>197633.45</v>
+        <v>197719.35</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-10-14 12:41:19</t>
+          <t>2026-10-15 12:29:25</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
@@ -1823,11 +1823,11 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>231203.62</v>
+        <v>231278.09</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:09</t>
+          <t>2026-10-15 12:28:41</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
@@ -1847,11 +1847,11 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>40247.89</v>
+        <v>40425.98</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-10-14 12:41:27</t>
+          <t>2026-10-15 12:28:22</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-10-10 05:25:46</t>
+          <t>2026-10-15 12:25:44</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
@@ -1895,11 +1895,11 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>31402.79</v>
+        <v>31402.82</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-10-14 12:37:54</t>
+          <t>2026-10-15 12:28:27</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
@@ -1967,11 +1967,11 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>10044.76</v>
+        <v>11188.25</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-10-14 12:41:23</t>
+          <t>2026-10-15 12:28:55</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
@@ -1991,11 +1991,11 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>25652.31</v>
+        <v>26841.79</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:05</t>
+          <t>2026-10-15 12:28:55</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
@@ -2015,11 +2015,11 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>26979.38</v>
+        <v>28156.77</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-10-14 12:41:08</t>
+          <t>2026-10-15 12:29:24</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>25967.83</v>
+        <v>26008.39</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:04</t>
+          <t>2026-10-15 12:26:55</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
@@ -2063,11 +2063,11 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>102895.96</v>
+        <v>103047.62</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-10-14 12:38:51</t>
+          <t>2026-10-15 12:29:19</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
@@ -2087,11 +2087,11 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>9347.77</v>
+        <v>9386.93</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-10-14 12:40:53</t>
+          <t>2026-10-15 12:26:56</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
@@ -2111,11 +2111,11 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>136792.42</v>
+        <v>136861.83</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-10-14 12:37:43</t>
+          <t>2026-10-15 12:21:52</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
@@ -2135,11 +2135,11 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>256072.92</v>
+        <v>256180.94</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-10-14 12:40:48</t>
+          <t>2026-10-15 12:29:34</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
@@ -2159,11 +2159,11 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>237611.17</v>
+        <v>237707.2</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-10-14 12:41:43</t>
+          <t>2026-10-15 12:29:25</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-10-14 12:42:27</t>
+          <t>2026-10-15 12:29:54</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>

--- a/data/kilometrajes_latest.xlsx
+++ b/data/kilometrajes_latest.xlsx
@@ -455,11 +455,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27018.36</v>
+        <v>27386.5</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-15 12:27:20</t>
+          <t>2026-10-16 12:11:22</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -467,7 +467,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -479,11 +479,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>358676.66</v>
+        <v>358848.25</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-15 12:26:53</t>
+          <t>2026-10-16 12:09:46</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -491,7 +491,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -503,11 +503,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>223022.72</v>
+        <v>224213.75</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-15 12:27:35</t>
+          <t>2026-10-16 12:04:32</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -515,7 +515,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -527,11 +527,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1711237.88</v>
+        <v>1712166.25</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-15 12:28:59</t>
+          <t>2026-10-16 12:05:46</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -539,7 +539,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -551,11 +551,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>144583.2</v>
+        <v>144677.78</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-15 12:28:03</t>
+          <t>2026-10-16 12:10:52</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -563,7 +563,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -575,11 +575,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>190799.89</v>
+        <v>190893.41</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-15 12:28:19</t>
+          <t>2026-10-16 12:11:10</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -587,7 +587,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -599,11 +599,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>791044.0600000001</v>
+        <v>792137.12</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-15 12:26:13</t>
+          <t>2026-10-16 12:11:25</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -611,7 +611,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -623,11 +623,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1347162</v>
+        <v>1347535.12</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-15 12:26:00</t>
+          <t>2026-10-16 12:10:37</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -635,7 +635,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -647,11 +647,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>179779.16</v>
+        <v>180065.51</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-15 12:21:45</t>
+          <t>2026-10-16 12:10:22</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -659,7 +659,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -671,11 +671,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1255796.75</v>
+        <v>1256987.88</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-15 12:25:30</t>
+          <t>2026-10-16 12:09:37</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -683,7 +683,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -695,11 +695,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>127232</v>
+        <v>127330.43</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-15 12:18:20</t>
+          <t>2026-10-16 12:10:30</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -707,7 +707,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -719,11 +719,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>360636.28</v>
+        <v>361817.12</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:16</t>
+          <t>2026-10-16 12:11:00</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -743,11 +743,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>201770.25</v>
+        <v>202231.58</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-10-15 12:27:48</t>
+          <t>2026-10-16 12:10:28</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -755,7 +755,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -767,11 +767,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>289063.88</v>
+        <v>289181.34</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:25</t>
+          <t>2026-10-16 12:08:13</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -791,11 +791,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>240941.14</v>
+        <v>242114.75</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-15 12:26:52</t>
+          <t>2026-10-16 12:09:28</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -803,7 +803,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -815,11 +815,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>596796.59</v>
+        <v>597292.03</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:27</t>
+          <t>2026-10-16 12:10:24</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -827,7 +827,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -839,11 +839,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>305353</v>
+        <v>306473.19</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-15 12:26:29</t>
+          <t>2026-10-16 12:08:57</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -851,7 +851,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -863,11 +863,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>22674.61</v>
+        <v>23882.73</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-10-15 12:27:35</t>
+          <t>2026-10-16 12:06:10</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -875,7 +875,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -887,11 +887,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>98659.88</v>
+        <v>98709.53</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-10-15 12:28:05</t>
+          <t>2026-10-16 12:10:49</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -899,7 +899,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -911,11 +911,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>208151.52</v>
+        <v>208983.3</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:25</t>
+          <t>2026-10-16 12:11:21</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -923,7 +923,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>200342.11</v>
+        <v>201035.55</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-10-15 12:23:32</t>
+          <t>2026-10-16 12:10:21</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -947,7 +947,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -959,11 +959,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>13063.5</v>
+        <v>14259.69</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-10-15 12:22:00</t>
+          <t>2026-10-16 12:10:23</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -971,7 +971,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -983,11 +983,11 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>214192.89</v>
+        <v>214225.2</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-10-15 12:28:08</t>
+          <t>2026-10-16 12:11:08</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -995,7 +995,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -1007,11 +1007,11 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>263697.23</v>
+        <v>263830.83</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-10-15 12:27:10</t>
+          <t>2026-10-16 12:09:20</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -1031,11 +1031,11 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5999.95</v>
+        <v>6921.07</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-10-15 12:27:12</t>
+          <t>2026-10-16 12:11:22</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -1055,11 +1055,11 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>235942.26</v>
+        <v>236161.2</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-10-15 12:26:52</t>
+          <t>2026-10-16 12:10:44</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -1079,11 +1079,11 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>619221.3100000001</v>
+        <v>620065.3100000001</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-10-15 12:27:07</t>
+          <t>2026-10-16 12:11:27</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
@@ -1103,11 +1103,11 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>164195.23</v>
+        <v>165129.75</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-10-15 12:27:51</t>
+          <t>2026-10-16 12:10:31</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
@@ -1127,11 +1127,11 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>44551.93</v>
+        <v>44630.13</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-10-15 12:28:25</t>
+          <t>2026-10-16 12:09:37</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
@@ -1151,11 +1151,11 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>394813.72</v>
+        <v>395184.06</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-10-15 12:27:14</t>
+          <t>2026-10-16 12:09:13</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
@@ -1175,11 +1175,11 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>389831.06</v>
+        <v>390763.03</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-10-15 12:27:17</t>
+          <t>2026-10-16 12:11:26</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
@@ -1199,11 +1199,11 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>7642.05</v>
+        <v>8806.879999999999</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-10-15 12:26:24</t>
+          <t>2026-10-16 12:11:11</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
@@ -1223,11 +1223,11 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>234155.99</v>
+        <v>234156.6</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-10-15 12:28:24</t>
+          <t>2026-10-15 22:28:53</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
@@ -1247,11 +1247,11 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>125005.98</v>
+        <v>125480.77</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-10-15 12:27:56</t>
+          <t>2026-10-16 12:10:39</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
@@ -1271,11 +1271,11 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>178974.57</v>
+        <v>178975.62</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-10-15 12:28:58</t>
+          <t>2026-10-16 01:28:32</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
@@ -1295,11 +1295,11 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>165663.38</v>
+        <v>166494.94</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:12</t>
+          <t>2026-10-16 12:09:58</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -1319,11 +1319,11 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>5378.04</v>
+        <v>6556.98</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-10-15 12:23:30</t>
+          <t>2026-10-16 12:11:17</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
@@ -1343,11 +1343,11 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>106400.66</v>
+        <v>106417.8</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-10-15 12:25:37</t>
+          <t>2026-10-16 12:10:04</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
@@ -1367,11 +1367,11 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>62665.29</v>
+        <v>62714.13</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-10-15 12:28:57</t>
+          <t>2026-10-16 12:10:52</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-10-15 12:28:09</t>
+          <t>2026-10-16 12:09:32</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-10-15 12:28:24</t>
+          <t>2026-10-16 12:08:58</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>468524.69</v>
+        <v>469010.25</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-10-15 12:26:42</t>
+          <t>2026-10-16 12:10:22</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -1511,11 +1511,11 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>187469.94</v>
+        <v>187507.28</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-10-15 12:28:09</t>
+          <t>2026-10-16 12:08:20</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
@@ -1535,11 +1535,11 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>374397.14</v>
+        <v>374617.27</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-10-15 12:26:17</t>
+          <t>2026-10-16 12:10:34</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
@@ -1559,11 +1559,11 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>5413.41</v>
+        <v>5439.78</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:25</t>
+          <t>2026-10-16 12:11:25</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-10-15 12:21:49</t>
+          <t>2026-10-16 12:09:18</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
@@ -1619,7 +1619,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -1631,11 +1631,11 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>553375.4399999999</v>
+        <v>553492.5600000001</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-10-15 12:24:08</t>
+          <t>2026-10-16 12:05:55</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
@@ -1655,11 +1655,11 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>92470.59</v>
+        <v>92913.55</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-10-15 12:27:06</t>
+          <t>2026-10-16 12:10:47</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
@@ -1679,11 +1679,11 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>91630.61</v>
+        <v>92565.61</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-10-15 12:27:34</t>
+          <t>2026-10-16 12:08:35</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
@@ -1703,11 +1703,11 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>317157.75</v>
+        <v>317289.88</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-10-15 12:23:37</t>
+          <t>2026-10-16 12:09:23</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
@@ -1727,11 +1727,11 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>184887.58</v>
+        <v>184962.53</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:13</t>
+          <t>2026-10-16 12:10:45</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
@@ -1775,11 +1775,11 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>35923.33</v>
+        <v>37003.76</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-10-15 12:26:32</t>
+          <t>2026-10-16 12:10:51</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
@@ -1799,11 +1799,11 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>197719.35</v>
+        <v>197802.41</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:25</t>
+          <t>2026-10-16 12:08:13</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
@@ -1823,11 +1823,11 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>231278.09</v>
+        <v>231360.27</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-10-15 12:28:41</t>
+          <t>2026-10-16 12:10:26</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-10-15 12:28:22</t>
+          <t>2026-10-16 12:09:29</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-10-15 12:25:44</t>
+          <t>2026-10-16 12:05:33</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
@@ -1895,11 +1895,11 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>31402.82</v>
+        <v>31402.85</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-10-15 12:28:27</t>
+          <t>2026-10-16 09:12:20</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
@@ -1967,11 +1967,11 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>11188.25</v>
+        <v>11212.37</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-10-15 12:28:55</t>
+          <t>2026-10-16 12:07:50</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
@@ -1991,11 +1991,11 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>26841.79</v>
+        <v>28022.12</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-10-15 12:28:55</t>
+          <t>2026-10-16 12:11:10</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
@@ -2015,11 +2015,11 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>28156.77</v>
+        <v>29338.68</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:24</t>
+          <t>2026-10-16 12:07:49</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>26008.39</v>
+        <v>26045.97</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-10-15 12:26:55</t>
+          <t>2026-10-16 12:10:55</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
@@ -2063,11 +2063,11 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>103047.62</v>
+        <v>103179.38</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:19</t>
+          <t>2026-10-16 12:11:17</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
@@ -2087,11 +2087,11 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>9386.93</v>
+        <v>9435.110000000001</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-10-15 12:26:56</t>
+          <t>2026-10-16 11:53:50</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
@@ -2111,11 +2111,11 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>136861.83</v>
+        <v>136963.27</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-10-15 12:21:52</t>
+          <t>2026-10-16 12:05:33</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
@@ -2135,11 +2135,11 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>256180.94</v>
+        <v>256257.41</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:34</t>
+          <t>2026-10-16 12:10:21</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
@@ -2159,11 +2159,11 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>237707.2</v>
+        <v>237902.52</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:25</t>
+          <t>2026-10-16 12:07:59</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-10-15 12:29:54</t>
+          <t>2026-10-16 12:11:54</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
